--- a/data/trans_dic/P57B3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57B3_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 22,29</t>
+          <t>16,37; 22,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,96; 27,56</t>
+          <t>23,15; 27,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,92; 24,65</t>
+          <t>21,13; 24,64</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,29; 40,02</t>
+          <t>9,86; 12,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 10,55</t>
+          <t>9,76; 12,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 31,3</t>
+          <t>10,13; 12,01</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,38</t>
+          <t>5,86; 9,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 9,75</t>
+          <t>6,32; 9,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,97</t>
+          <t>6,49; 9,27</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 38,09</t>
+          <t>10,8; 13,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 13,3</t>
+          <t>12,63; 14,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,41; 26,8</t>
+          <t>12,07; 13,51</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>99073</t>
+          <t>111937</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>187778</t>
+          <t>208147</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286851</t>
+          <t>320085</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83996; 114569</t>
+          <t>94560; 130086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>172909; 207499</t>
+          <t>189680; 229199</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265083; 312321</t>
+          <t>295216; 344189</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>464649</t>
+          <t>250113</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>201319</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>665968</t>
+          <t>489347</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>235573; 916112</t>
+          <t>219816; 283607</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146179; 235839</t>
+          <t>211612; 267980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>428213; 1416540</t>
+          <t>445412; 528074</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45612</t>
+          <t>54989</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>57425</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97005</t>
+          <t>112415</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34278; 60635</t>
+          <t>41708; 69757</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41529; 64353</t>
+          <t>46403; 71333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81395; 117209</t>
+          <t>93869; 133995</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>504807</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1049824</t>
+          <t>921846</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>380475; 1313966</t>
+          <t>380052; 459944</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>362643; 485113</t>
+          <t>470301; 542552</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>809910; 1902223</t>
+          <t>874162; 978274</t>
         </is>
       </c>
     </row>
